--- a/staff_forms/001_onboarding_feedback_questionnaire--staff_forms.xlsx
+++ b/staff_forms/001_onboarding_feedback_questionnaire--staff_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Onboarding duration</t>
+          <t>How would you rate the clarity of our onboarding process?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Onboarding process satisfaction</t>
+          <t>What were some challenges you faced during onboarding?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Onboarding process alignment with company values</t>
+          <t>How engaging was your onboarding experience?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What did we do well?</t>
+          <t>What did we do well that was different from others?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Onboarding process clarity</t>
+          <t>How can we improve onboarding process communication?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How can we improve onboarding process?</t>
+          <t>Was your onboarding experience unique?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What was your first week like?</t>
+          <t>What areas of the onboarding process did you find difficult to adjust to?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Onboarding process communication</t>
+          <t>What did we do well that was not typically part of our onboarding process?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Was your onboarding experience unique?</t>
+          <t>How well did the onboarding process align with company values?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What did you find difficult?</t>
+          <t>How can we make onboarding duration more effective?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,310 +778,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What can we do to improve onboarding process for next new employee?</t>
+          <t>What suggestions do you have for us to improve the onboarding process for future new employees?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Onboarding process consistency</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>How can we improve onboarding process?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Was your onboarding process aligned with company culture?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Onboarding process engagement</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>What can we do better next time?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Onboarding process uniqueness</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>How can we improve onboarding process?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Onboarding process clarity</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Onboarding duration</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What did we do well that was different from others?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Was there a dedicated onboarding program in place?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>How can we improve onboarding process?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Onboarding process communication</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,85 +827,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_3_choices</t>
+          <t>onboarding_feedback_questionnaire_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_clear</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Very satisfied'}</t>
+          <t>Very clear</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_3_choices</t>
+          <t>onboarding_feedback_questionnaire_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'satisfied'}</t>
+          <t>somewhat_clear</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Satisfied'}</t>
+          <t>Somewhat clear</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_3_choices</t>
+          <t>onboarding_feedback_questionnaire_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>not_very_clear</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Not very clear</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_3_choices</t>
+          <t>onboarding_feedback_questionnaire_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'unsatisfied'}</t>
+          <t>not_at_all_clear</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Unsatisfied'}</t>
+          <t>Not at all clear</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_3_choices</t>
+          <t>onboarding_feedback_questionnaire_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'very_unsatisfied'}</t>
+          <t>engaging</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Very unsatisfied'}</t>
+          <t>Engaging</t>
         </is>
       </c>
     </row>
@@ -1216,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'aligns_closely'}</t>
+          <t>somewhat_engaging</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Aligns closely'}</t>
+          <t>Somewhat engaging</t>
         </is>
       </c>
     </row>
@@ -1233,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_aligns'}</t>
+          <t>not_engaging</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat aligns'}</t>
+          <t>Not engaging</t>
         </is>
       </c>
     </row>
@@ -1250,97 +951,97 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'not_very_well'}</t>
+          <t>not_at_all_engaging</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Not very well'}</t>
+          <t>Not at all engaging</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_4_choices</t>
+          <t>onboarding_feedback_questionnaire_7_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all'}</t>
+          <t>very_unique</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all'}</t>
+          <t>Very unique</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_6_choices</t>
+          <t>onboarding_feedback_questionnaire_7_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'very_clear'}</t>
+          <t>somewhat_unique</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Very clear'}</t>
+          <t>Somewhat unique</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_6_choices</t>
+          <t>onboarding_feedback_questionnaire_7_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_clear'}</t>
+          <t>not_very_unique</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat clear'}</t>
+          <t>Not very unique</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_6_choices</t>
+          <t>onboarding_feedback_questionnaire_7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'not_very_clear'}</t>
+          <t>not_at_all_unique</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Not very clear'}</t>
+          <t>Not at all unique</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_6_choices</t>
+          <t>onboarding_feedback_questionnaire_8_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all_clear'}</t>
+          <t>adjusting_to_new_technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Not at all clear'}</t>
+          <t>Adjusting to new technology</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>adjusting_to_new_processes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Adjusting to new processes</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>building_relationships</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Building relationships</t>
         </is>
       </c>
     </row>
@@ -1386,675 +1087,80 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'average'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Average'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_8_choices</t>
+          <t>onboarding_feedback_questionnaire_10_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>aligns_closely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Aligns closely</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_8_choices</t>
+          <t>onboarding_feedback_questionnaire_10_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'very_poor'}</t>
+          <t>somewhat_aligns</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Very poor'}</t>
+          <t>Somewhat aligns</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_9_choices</t>
+          <t>onboarding_feedback_questionnaire_10_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'communicated_clearly'}</t>
+          <t>not_very_well</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Communicated clearly'}</t>
+          <t>Not very well</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>onboarding_feedback_questionnaire_9_choices</t>
+          <t>onboarding_feedback_questionnaire_10_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'communicated_somewhat'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Communicated somewhat'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_9_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'value':_'not_communicated_clearly'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'value': 'Not communicated clearly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_9_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'value':_'not_at_all_communicated'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'value': 'Not at all communicated'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_10_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'value':_true}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'value': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_10_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'value':_false}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'value': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_11_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'value':_'adjusting_to_new_technology'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'value': 'Adjusting to new technology'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_11_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'value':_'adjusting_to_new_processes'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'value': 'Adjusting to new processes'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_11_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'value':_'building_relationships'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'value': 'Building relationships'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_11_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'value': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_13_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'value':_'very_consistent'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'value': 'Very consistent'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_13_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'value':_'somewhat_consistent'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'value': 'Somewhat consistent'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_13_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'value':_'not_very_consistent'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'value': 'Not very consistent'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_13_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'value':_'not_at_all_consistent'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'value': 'Not at all consistent'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_15_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'value':_true}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'value': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_15_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'value':_false}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'value': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_16_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'value':_'engaging'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'value': 'Engaging'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_16_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'value':_'somewhat_engaging'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'value': 'Somewhat engaging'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_16_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'value':_'not_engaging'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'value': 'Not engaging'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_16_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'value':_'not_at_all_engaging'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'value': 'Not at all engaging'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_18_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'value':_'very_unique'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'value': 'Very unique'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_18_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'value':_'somewhat_unique'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'value': 'Somewhat unique'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_18_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'value':_'not_very_unique'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'value': 'Not very unique'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_18_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'value':_'not_at_all_unique'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'value': 'Not at all unique'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_20_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'value':_'very_clear'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'value': 'Very clear'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_20_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'value':_'somewhat_clear'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'value': 'Somewhat clear'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_20_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'value':_'not_very_clear'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'value': 'Not very clear'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_20_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'value':_'not_at_all_clear'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'value': 'Not at all clear'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_21_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'value':_'short'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'value': 'Short'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_21_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'value':_'average'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'value': 'Average'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_21_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'value':_'long'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'value': 'Long'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_23_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'value':_true}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'value': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_23_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'value':_false}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'value': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_25_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'value':_'communicated_clearly'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'value': 'Communicated clearly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_25_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>{'value':_'communicated_somewhat'}</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>{'value': 'Communicated somewhat'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_25_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>{'value':_'not_communicated_clearly'}</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>{'value': 'Not communicated clearly'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>onboarding_feedback_questionnaire_25_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>{'value':_'not_at_all_communicated'}</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>{'value': 'Not at all communicated'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
